--- a/astro-site/public/dl/ghost-kitchen-checklist-templates/09-cash-drawer-opening-closing.xlsx
+++ b/astro-site/public/dl/ghost-kitchen-checklist-templates/09-cash-drawer-opening-closing.xlsx
@@ -845,11 +845,11 @@
     <row r="5">
       <c r="A5" s="4" t="n"/>
     </row>
-    <row r="6" ht="32" customHeight="1">
+    <row r="6" ht="77" customHeight="1">
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="29" t="inlineStr">
         <is>
-          <t>▸ The daily cash count: starting bank, drawer count by denomination, POS Z report and over/short — plus the monthly log to see at a glance which days didn't balance.</t>
+          <t>▸ The daily cash count: starting bank, drawer count by denomination, POS Z report and over/short — plus the monthly log to see at a glance which days didn't balance. In a delivery-only kitchen the app orders are prepaid and paid out by each app (reconcile them against each app's payout report, 01 "Kitchen Closing", task #18): use this file for what is paid at your own counter — walk-in pickup, phone or own-website orders paid on pickup.</t>
         </is>
       </c>
     </row>
